--- a/output/2026年5月/2026年5月党费收缴明细表.xlsx
+++ b/output/2026年5月/2026年5月党费收缴明细表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年5月党费收缴明细表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年五月党费收缴明细表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -509,7 +509,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新疆大学计算机科学与技术学院2026年5月党费收缴明细表</t>
+          <t>计算机科学与技术学院2026年五月党费收缴明细表</t>
         </is>
       </c>
     </row>
@@ -668,13 +668,13 @@
         <v>45</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>997</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>174.5</v>
+        <v>169.7</v>
       </c>
     </row>
     <row r="5">
